--- a/chance.son.xlsx
+++ b/chance.son.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\slck\Kaptan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B53669-3893-4C1B-BF6B-F2F8DE8D9854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837E08B1-7AD3-4C7E-9CB1-90CDA21BFB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="223">
   <si>
     <t>TEK</t>
   </si>
@@ -2092,105 +2092,6 @@
   </si>
   <si>
     <t xml:space="preserve">  -&gt; YOK : %35.40 (57 Kez)</t>
-  </si>
-  <si>
-    <t>%30.77 ihtimalle : 3 Sıcak - 2 Orta - 0 Soğuk</t>
-  </si>
-  <si>
-    <t>%30.77 ihtimalle : 2 Sıcak - 2 Orta - 1 Soğuk</t>
-  </si>
-  <si>
-    <t>%34.21 ihtimalle : 2 Alt - 3 Üst</t>
-  </si>
-  <si>
-    <t>%26.32 ihtimalle : 3 Alt - 2 Üst</t>
-  </si>
-  <si>
-    <t>%35.59 ihtimalle : 2 Tek - 3 Çift</t>
-  </si>
-  <si>
-    <t>%32.20 ihtimalle : 3 Tek - 2 Çift</t>
-  </si>
-  <si>
-    <t>%100.00 ihtimalle : 2 Birler - 3 Onlar - 0 Yirmiler - 0 Otuzlar</t>
-  </si>
-  <si>
-    <t>%51.32 ihtimalle : YOK ardışık</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 Tek - 3 Çift: %33.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 1 Tek - 4 Çift: %22.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 4 Tek - 1 Çift: %22.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 3 Tek - 2 Çift: %22.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 Alt - 3 Üst: %66.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 B - 1 O - 2 Y - 0 Ot: %16.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 1 B - 1 O - 2 Y - 1 Ot: %16.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 1 B - 1 O - 1 Y - 2 Ot: %11.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 B - 1 O - 1 Y - 1 Ot: %11.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; YOK: %55.56 ardışık</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; VAR: %77.78 devir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 4 Tek - 1 Çift: %34.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 Tek - 3 Çift: %26.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 3 Tek - 2 Çift: %21.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 5 Tek - 0 Çift: %13.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 Alt - 3 Üst: %43.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 3 Alt - 2 Üst: %21.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 1 Alt - 4 Üst: %17.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 B - 2 O - 1 Y - 0 Ot: %17.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 1 B - 2 O - 2 Y - 0 Ot: %17.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 1 B - 1 O - 2 Y - 1 Ot: %8.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; 2 B - 0 O - 3 Y - 0 Ot: %8.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; YOK: %65.22 ardışık</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; YOK: %52.17 devir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  -&gt; VAR: %47.83 devir</t>
   </si>
 </sst>
 </file>
@@ -2675,7 +2576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2800,6 +2701,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3211,7 +3119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T163"/>
+  <dimension ref="A1:T164"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="5" width="3.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -3224,328 +3132,295 @@
     <col min="20" max="20" width="111.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1">
-      <c r="T1" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
+    <row r="1" spans="1:20" ht="15" thickBot="1"/>
     <row r="2" spans="1:20" ht="15" thickBot="1">
       <c r="A2" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>15</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" thickBot="1">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15" thickBot="1">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
         <v>5</v>
       </c>
-      <c r="H3">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="J3">
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="K3">
+      <c r="K4">
         <v>7</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>9</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <f>COUNTIF(A:E,26)</f>
         <v>22</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>2</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>6</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>8</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>10</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15" thickBot="1">
-      <c r="A4" s="1">
+    <row r="5" spans="1:20" ht="15" thickBot="1">
+      <c r="A5" s="1">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C5" s="1">
         <v>22</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D5" s="1">
         <v>25</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E5" s="1">
         <v>26</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1">
+      <c r="F5" s="1"/>
+      <c r="G5" s="1">
         <v>8</v>
       </c>
-      <c r="H4">
+      <c r="H5">
         <f>COUNTIF($A:$E,1)</f>
-        <v>26</v>
-      </c>
-      <c r="I4">
+        <v>27</v>
+      </c>
+      <c r="I5">
         <f>COUNTIF($A:$E,3)</f>
         <v>22</v>
       </c>
-      <c r="J4">
+      <c r="J5">
         <f>COUNTIF($A:$E,5)</f>
         <v>30</v>
       </c>
-      <c r="K4">
+      <c r="K5">
         <f>COUNTIF($A:$E,7)</f>
         <v>26</v>
       </c>
-      <c r="L4">
+      <c r="L5">
         <f>COUNTIF($A:$E,9)</f>
         <v>23</v>
       </c>
-      <c r="N4">
+      <c r="N5">
         <f>COUNTIF($A:$E,2)</f>
         <v>31</v>
       </c>
-      <c r="O4">
+      <c r="O5">
         <f>COUNTIF($A:$E,4)</f>
         <v>21</v>
       </c>
-      <c r="P4">
+      <c r="P5">
         <f>COUNTIF($A:$E,6)</f>
         <v>22</v>
       </c>
-      <c r="Q4">
+      <c r="Q5">
         <f>COUNTIF($A:$E,8)</f>
         <v>34</v>
       </c>
-      <c r="R4">
+      <c r="R5">
         <f>COUNTIF($A:$E,10)</f>
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15" thickBot="1">
-      <c r="A5" s="1">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>17</v>
-      </c>
-      <c r="L5">
-        <v>19</v>
-      </c>
-      <c r="N5">
-        <v>12</v>
-      </c>
-      <c r="O5">
-        <v>14</v>
-      </c>
-      <c r="P5">
-        <v>16</v>
-      </c>
-      <c r="Q5">
-        <v>18</v>
-      </c>
-      <c r="R5">
-        <v>20</v>
-      </c>
-      <c r="T5" t="s">
-        <v>151</v>
-      </c>
-    </row>
     <row r="6" spans="1:20" ht="15" thickBot="1">
       <c r="A6" s="1">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="N6">
+        <v>12</v>
+      </c>
+      <c r="O6">
+        <v>14</v>
+      </c>
+      <c r="P6">
+        <v>16</v>
+      </c>
+      <c r="Q6">
+        <v>18</v>
+      </c>
+      <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="T6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15" thickBot="1">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <v>7</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C7" s="1">
         <v>24</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D7" s="1">
         <v>30</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E7" s="1">
         <v>32</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G7" s="14">
         <v>12</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <f>COUNTIF($A:$E,11)</f>
         <v>18</v>
       </c>
-      <c r="I6">
+      <c r="I7">
         <f>COUNTIF($A:$E,13)</f>
         <v>19</v>
       </c>
-      <c r="J6">
+      <c r="J7">
         <f>COUNTIF($A:$E,15)</f>
-        <v>27</v>
-      </c>
-      <c r="K6">
+        <v>28</v>
+      </c>
+      <c r="K7">
         <f>COUNTIF($A:$E,17)</f>
         <v>19</v>
       </c>
-      <c r="L6">
+      <c r="L7">
         <f>COUNTIF($A:$E,19)</f>
         <v>29</v>
       </c>
-      <c r="N6">
+      <c r="N7">
         <f>COUNTIF($A:$E,12)</f>
         <v>19</v>
       </c>
-      <c r="O6">
+      <c r="O7">
         <f>COUNTIF($A:$E,14)</f>
         <v>20</v>
       </c>
-      <c r="P6">
+      <c r="P7">
         <f>COUNTIF($A:$E,16)</f>
         <v>22</v>
       </c>
-      <c r="Q6">
+      <c r="Q7">
         <f>COUNTIF($A:$E,18)</f>
         <v>24</v>
       </c>
-      <c r="R6">
+      <c r="R7">
         <f>COUNTIF($A:$E,20)</f>
         <v>28</v>
       </c>
-      <c r="T6" t="s">
+      <c r="T7" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" thickBot="1">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1">
-        <v>34</v>
-      </c>
-      <c r="G7" s="14">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>23</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>29</v>
-      </c>
-      <c r="N7">
-        <v>22</v>
-      </c>
-      <c r="O7">
-        <v>24</v>
-      </c>
-      <c r="P7">
-        <v>26</v>
-      </c>
-      <c r="Q7">
-        <v>28</v>
-      </c>
-      <c r="R7">
-        <v>30</v>
-      </c>
-      <c r="T7" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15" thickBot="1">
@@ -3556,257 +3431,286 @@
         <v>7</v>
       </c>
       <c r="C8" s="1">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>34</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>25</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>29</v>
+      </c>
+      <c r="N8">
+        <v>22</v>
+      </c>
+      <c r="O8">
+        <v>24</v>
+      </c>
+      <c r="P8">
+        <v>26</v>
+      </c>
+      <c r="Q8">
+        <v>28</v>
+      </c>
+      <c r="R8">
+        <v>30</v>
+      </c>
+      <c r="T8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15" thickBot="1">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
         <v>13</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>14</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E9" s="1">
         <v>29</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G9" s="14">
         <v>6</v>
       </c>
-      <c r="H8">
+      <c r="H9">
         <f>COUNTIF($A:$E,21)</f>
         <v>23</v>
       </c>
-      <c r="I8">
+      <c r="I9">
         <f>COUNTIF($A:$E,23)</f>
         <v>18</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <f>COUNTIF($A:$E,25)</f>
         <v>24</v>
       </c>
-      <c r="K8">
+      <c r="K9">
         <f>COUNTIF($A:$E,27)</f>
         <v>21</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <f>COUNTIF($A:$E,29)</f>
-        <v>27</v>
-      </c>
-      <c r="N8">
+        <v>28</v>
+      </c>
+      <c r="N9">
         <f>COUNTIF($A:$E,22)</f>
-        <v>37</v>
-      </c>
-      <c r="O8">
+        <v>38</v>
+      </c>
+      <c r="O9">
         <f>COUNTIF($A:$E,24)</f>
         <v>19</v>
       </c>
-      <c r="P8">
+      <c r="P9">
         <f>COUNTIF($A:$E,26)</f>
         <v>22</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <f>COUNTIF($A:$E,28)</f>
         <v>17</v>
       </c>
-      <c r="R8">
+      <c r="R9">
         <f>COUNTIF($A:$E,30)</f>
-        <v>18</v>
-      </c>
-      <c r="T8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1">
-        <v>33</v>
-      </c>
-      <c r="G9" s="14">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>31</v>
-      </c>
-      <c r="I9">
-        <v>33</v>
-      </c>
-      <c r="N9">
-        <v>32</v>
-      </c>
-      <c r="O9">
-        <v>34</v>
-      </c>
-      <c r="T9" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" thickBot="1">
       <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>33</v>
+      </c>
+      <c r="N10">
+        <v>32</v>
+      </c>
+      <c r="O10">
+        <v>34</v>
+      </c>
+      <c r="T10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15" thickBot="1">
+      <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11" s="1">
         <v>19</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>22</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>30</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G11" s="14">
         <v>5</v>
       </c>
-      <c r="H10">
+      <c r="H11">
         <f>COUNTIF($A:$E,31)</f>
         <v>24</v>
       </c>
-      <c r="I10">
+      <c r="I11">
         <f>COUNTIF($A:$E,33)</f>
         <v>27</v>
       </c>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="N10">
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="N11">
         <f>COUNTIF($A:$E,32)</f>
         <v>25</v>
       </c>
-      <c r="O10">
+      <c r="O11">
         <f>COUNTIF($A:$E,34)</f>
         <v>25</v>
       </c>
-      <c r="P10" s="52"/>
-      <c r="T10" t="s">
+      <c r="P11" s="52"/>
+      <c r="T11" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="15" thickBot="1">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1">
-        <v>29</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="14">
-        <v>10</v>
-      </c>
-      <c r="T11" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" thickBot="1">
       <c r="A12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D12" s="1">
         <v>22</v>
       </c>
       <c r="E12" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" thickBot="1">
       <c r="A13" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15" thickBot="1">
       <c r="A14" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B14" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15" thickBot="1">
       <c r="A15" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1">
         <v>21</v>
       </c>
       <c r="E15" s="1">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15" thickBot="1">
@@ -3814,58 +3718,47 @@
         <v>7</v>
       </c>
       <c r="B16" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="14">
         <v>14</v>
       </c>
-      <c r="T16" s="4" t="s">
-        <v>168</v>
+      <c r="T16" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15" thickBot="1">
       <c r="A17" s="1">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1">
         <v>22</v>
       </c>
       <c r="E17" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="14">
-        <v>13</v>
-      </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
+        <v>14</v>
+      </c>
       <c r="T17" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15" thickBot="1">
@@ -3873,20 +3766,20 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1">
         <v>20</v>
       </c>
-      <c r="C18" s="1">
-        <v>26</v>
-      </c>
       <c r="D18" s="1">
+        <v>22</v>
+      </c>
+      <c r="E18" s="1">
         <v>27</v>
-      </c>
-      <c r="E18" s="1">
-        <v>34</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H18" s="54"/>
       <c r="I18" s="54"/>
@@ -3900,28 +3793,28 @@
       <c r="Q18" s="52"/>
       <c r="R18" s="52"/>
       <c r="T18" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15" thickBot="1">
       <c r="A19" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1">
+        <v>26</v>
+      </c>
+      <c r="D19" s="1">
         <v>27</v>
-      </c>
-      <c r="D19" s="1">
-        <v>31</v>
       </c>
       <c r="E19" s="1">
         <v>34</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H19" s="54"/>
       <c r="I19" s="54"/>
@@ -3934,13 +3827,16 @@
       <c r="P19" s="52"/>
       <c r="Q19" s="52"/>
       <c r="R19" s="52"/>
+      <c r="T19" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="20" spans="1:20" ht="15" thickBot="1">
       <c r="A20" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1">
         <v>27</v>
@@ -3949,11 +3845,11 @@
         <v>31</v>
       </c>
       <c r="E20" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H20" s="54"/>
       <c r="I20" s="54"/>
@@ -3966,35 +3862,32 @@
       <c r="P20" s="52"/>
       <c r="Q20" s="52"/>
       <c r="R20" s="52"/>
-      <c r="T20" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="21" spans="1:20" ht="15" thickBot="1">
       <c r="A21" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="14">
-        <v>6</v>
-      </c>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
+        <v>8</v>
+      </c>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
       <c r="M21" s="52"/>
       <c r="N21" s="52"/>
       <c r="O21" s="52"/>
@@ -4002,28 +3895,28 @@
       <c r="Q21" s="52"/>
       <c r="R21" s="52"/>
       <c r="T21" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15" thickBot="1">
       <c r="A22" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D22" s="1">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H22" s="52"/>
       <c r="I22" s="52"/>
@@ -4037,59 +3930,59 @@
       <c r="Q22" s="52"/>
       <c r="R22" s="52"/>
       <c r="T22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15" thickBot="1">
       <c r="A23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="1">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1">
         <v>20</v>
       </c>
-      <c r="C23" s="1">
-        <v>25</v>
-      </c>
       <c r="D23" s="1">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E23" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="14">
-        <v>13</v>
-      </c>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
+        <v>12</v>
+      </c>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
       <c r="N23" s="52"/>
       <c r="O23" s="52"/>
       <c r="P23" s="52"/>
       <c r="Q23" s="52"/>
       <c r="R23" s="52"/>
-      <c r="T23" s="4" t="s">
-        <v>164</v>
+      <c r="T23" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15" thickBot="1">
       <c r="A24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E24" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="14">
@@ -4107,28 +4000,28 @@
       <c r="Q24" s="52"/>
       <c r="R24" s="52"/>
       <c r="T24" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15" thickBot="1">
       <c r="A25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C25" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H25" s="54"/>
       <c r="I25" s="54"/>
@@ -4141,59 +4034,64 @@
       <c r="P25" s="52"/>
       <c r="Q25" s="52"/>
       <c r="R25" s="52"/>
-      <c r="T25" t="s">
-        <v>166</v>
+      <c r="T25" s="4" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15" thickBot="1">
       <c r="A26" s="1">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1">
         <v>6</v>
       </c>
-      <c r="B26" s="1">
-        <v>17</v>
-      </c>
       <c r="C26" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="14">
-        <v>9</v>
-      </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="52"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="52"/>
+      <c r="R26" s="52"/>
       <c r="T26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15" thickBot="1">
       <c r="A27" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B27" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D27" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
@@ -4201,26 +4099,29 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
+      <c r="T27" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="28" spans="1:20" ht="15" thickBot="1">
       <c r="A28" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B28" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E28" s="1">
         <v>34</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4228,25 +4129,22 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
-      <c r="T28" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="29" spans="1:20" ht="15" thickBot="1">
       <c r="A29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" s="1">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="14">
@@ -4259,28 +4157,28 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="T29" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15" thickBot="1">
       <c r="A30" s="1">
+        <v>1</v>
+      </c>
+      <c r="B30" s="1">
         <v>2</v>
       </c>
-      <c r="B30" s="1">
-        <v>6</v>
-      </c>
       <c r="C30" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
         <v>19</v>
-      </c>
-      <c r="E30" s="1">
-        <v>24</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -4289,28 +4187,28 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="T30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="15" thickBot="1">
       <c r="A31" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31" s="1">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
@@ -4318,368 +4216,374 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
-      <c r="T31" s="4"/>
+      <c r="T31" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="32" spans="1:20" ht="15" thickBot="1">
       <c r="A32" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B32" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D32" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E32" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="14">
-        <v>3</v>
-      </c>
-      <c r="T32" t="s">
-        <v>132</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="T32" s="4"/>
     </row>
     <row r="33" spans="1:20" ht="15" thickBot="1">
       <c r="A33" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B33" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C33" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D33" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="14">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T33" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15" thickBot="1">
       <c r="A34" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B34" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1">
         <v>12</v>
       </c>
       <c r="D34" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E34" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="14">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="15" thickBot="1">
       <c r="A35" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B35" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C35" s="1">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D35" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E35" s="1">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="14">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="T35" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15" thickBot="1">
       <c r="A36" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B36" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C36" s="1">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D36" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E36" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="14">
-        <v>9</v>
-      </c>
-      <c r="T36" s="4" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="15" thickBot="1">
       <c r="A37" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B37" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C37" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D37" s="1">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1">
         <v>29</v>
-      </c>
-      <c r="E37" s="1">
-        <v>31</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="15" thickBot="1">
       <c r="A38" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B38" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E38" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="14">
-        <v>14</v>
-      </c>
-      <c r="T38" t="s">
-        <v>176</v>
+        <v>13</v>
+      </c>
+      <c r="T38" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="15" thickBot="1">
       <c r="A39" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D39" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E39" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="14">
         <v>14</v>
       </c>
-      <c r="T39" s="49" t="s">
-        <v>177</v>
+      <c r="T39" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15" thickBot="1">
       <c r="A40" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B40" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E40" s="1">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="14">
-        <v>10</v>
-      </c>
-      <c r="T40" s="34" t="s">
-        <v>178</v>
+        <v>14</v>
+      </c>
+      <c r="T40" s="49" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="15" thickBot="1">
       <c r="A41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E41" s="1">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="15" thickBot="1">
       <c r="A42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C42" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E42" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" s="34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="15" thickBot="1">
       <c r="A43" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B43" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C43" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T43" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="15" thickBot="1">
       <c r="A44" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B44" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C44" s="1">
         <v>24</v>
       </c>
       <c r="D44" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E44" s="1">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T44" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="15" thickBot="1">
       <c r="A45" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C45" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D45" s="1">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E45" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" s="34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="15" thickBot="1">
       <c r="A46" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B46" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D46" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E46" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="14">
         <v>12</v>
       </c>
       <c r="T46" s="34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="15" thickBot="1">
       <c r="A47" s="1">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B47" s="1">
         <v>20</v>
@@ -4688,199 +4592,202 @@
         <v>24</v>
       </c>
       <c r="D47" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E47" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="14">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="T47" s="34" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="15" thickBot="1">
       <c r="A48" s="1">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B48" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C48" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D48" s="1">
         <v>28</v>
       </c>
       <c r="E48" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="14">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1">
       <c r="A49" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B49" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C49" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1">
         <v>28</v>
       </c>
       <c r="E49" s="1">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1">
       <c r="A50" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B50" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C50" s="1">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E50" s="1">
         <v>33</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1">
       <c r="A51" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B51" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C51" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D51" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E51" s="1">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1">
       <c r="A52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D52" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E52" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1">
       <c r="A53" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B53" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C53" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D53" s="1">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1">
       <c r="A54" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B54" s="1">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C54" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D54" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E54" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1">
       <c r="A55" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B55" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C55" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D55" s="1">
+        <v>26</v>
+      </c>
+      <c r="E55" s="1">
         <v>29</v>
-      </c>
-      <c r="E55" s="1">
-        <v>34</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1">
       <c r="A56" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B56" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D56" s="1">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E56" s="1">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="14">
@@ -4889,191 +4796,191 @@
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1">
       <c r="A57" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B57" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C57" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D57" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E57" s="1">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1">
       <c r="A58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B58" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C58" s="1">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D58" s="1">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E58" s="1">
         <v>34</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1">
       <c r="A59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B59" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D59" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E59" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1">
       <c r="A60" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C60" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D60" s="1">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E60" s="1">
         <v>33</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1">
       <c r="A61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B61" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C61" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D61" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E61" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="14">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1">
       <c r="A62" s="1">
+        <v>1</v>
+      </c>
+      <c r="B62" s="1">
         <v>3</v>
       </c>
-      <c r="B62" s="1">
-        <v>6</v>
-      </c>
       <c r="C62" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E62" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1">
       <c r="A63" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B63" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C63" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D63" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E63" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1">
       <c r="A64" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B64" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D64" s="1">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E64" s="1">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1">
       <c r="A65" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B65" s="1">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C65" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D65" s="1">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E65" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1">
@@ -5081,62 +4988,62 @@
         <v>8</v>
       </c>
       <c r="B66" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C66" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D66" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E66" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1">
       <c r="A67" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B67" s="1">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C67" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D67" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E67" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1">
       <c r="A68" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B68" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C68" s="1">
+        <v>19</v>
+      </c>
+      <c r="D68" s="1">
+        <v>20</v>
+      </c>
+      <c r="E68" s="1">
         <v>22</v>
-      </c>
-      <c r="D68" s="1">
-        <v>25</v>
-      </c>
-      <c r="E68" s="1">
-        <v>27</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1">
@@ -5144,58 +5051,58 @@
         <v>5</v>
       </c>
       <c r="B69" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C69" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D69" s="1">
         <v>25</v>
       </c>
       <c r="E69" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1">
       <c r="A70" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B70" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D70" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E70" s="1">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1">
       <c r="A71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B71" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C71" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D71" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E71" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="14">
@@ -5207,188 +5114,188 @@
         <v>1</v>
       </c>
       <c r="B72" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C72" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D72" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E72" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1">
       <c r="A73" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B73" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C73" s="1">
+        <v>7</v>
+      </c>
+      <c r="D73" s="1">
+        <v>14</v>
+      </c>
+      <c r="E73" s="1">
         <v>20</v>
-      </c>
-      <c r="D73" s="1">
-        <v>27</v>
-      </c>
-      <c r="E73" s="1">
-        <v>33</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1">
       <c r="A74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C74" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D74" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1">
         <v>33</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1">
       <c r="A75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B75" s="1">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C75" s="1">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D75" s="1">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E75" s="1">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1">
       <c r="A76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" s="1">
+        <v>7</v>
+      </c>
+      <c r="C76" s="1">
         <v>8</v>
       </c>
-      <c r="C76" s="1">
+      <c r="D76" s="1">
+        <v>11</v>
+      </c>
+      <c r="E76" s="1">
         <v>22</v>
-      </c>
-      <c r="D76" s="1">
-        <v>25</v>
-      </c>
-      <c r="E76" s="1">
-        <v>29</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1">
       <c r="A77" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B77" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C77" s="1">
         <v>22</v>
       </c>
       <c r="D77" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E77" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1">
       <c r="A78" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B78" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C78" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D78" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E78" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1">
       <c r="A79" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B79" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C79" s="1">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D79" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E79" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1">
       <c r="A80" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B80" s="1">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C80" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D80" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E80" s="1">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" thickBot="1">
@@ -5399,59 +5306,59 @@
         <v>6</v>
       </c>
       <c r="C81" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D81" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E81" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" thickBot="1">
       <c r="A82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B82" s="1">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1">
         <v>12</v>
       </c>
-      <c r="C82" s="1">
-        <v>13</v>
-      </c>
       <c r="D82" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E82" s="1">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" thickBot="1">
       <c r="A83" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B83" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C83" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D83" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E83" s="1">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1">
@@ -5459,293 +5366,293 @@
         <v>4</v>
       </c>
       <c r="B84" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C84" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D84" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E84" s="1">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" thickBot="1">
       <c r="A85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B85" s="1">
         <v>5</v>
       </c>
       <c r="C85" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D85" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E85" s="1">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1">
       <c r="A86" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B86" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C86" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D86" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E86" s="1">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" thickBot="1">
       <c r="A87" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B87" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C87" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D87" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E87" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" thickBot="1">
       <c r="A88" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B88" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D88" s="1">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E88" s="1">
         <v>31</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" thickBot="1">
       <c r="A89" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B89" s="1">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C89" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D89" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1">
         <v>31</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="14">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" thickBot="1">
       <c r="A90" s="1">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B90" s="1">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C90" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D90" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E90" s="1">
         <v>31</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" thickBot="1">
       <c r="A91" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B91" s="1">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C91" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D91" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E91" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1">
       <c r="A92" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B92" s="1">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C92" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D92" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E92" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1">
       <c r="A93" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B93" s="1">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C93" s="1">
+        <v>17</v>
+      </c>
+      <c r="D93" s="1">
         <v>21</v>
       </c>
-      <c r="D93" s="1">
-        <v>25</v>
-      </c>
       <c r="E93" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1">
       <c r="A94" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B94" s="1">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C94" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D94" s="1">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E94" s="1">
         <v>34</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1">
       <c r="A95" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B95" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C95" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D95" s="1">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E95" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1">
       <c r="A96" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B96" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C96" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D96" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E96" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1">
       <c r="A97" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B97" s="1">
+        <v>10</v>
+      </c>
+      <c r="C97" s="1">
+        <v>13</v>
+      </c>
+      <c r="D97" s="1">
+        <v>19</v>
+      </c>
+      <c r="E97" s="1">
         <v>22</v>
-      </c>
-      <c r="C97" s="1">
-        <v>23</v>
-      </c>
-      <c r="D97" s="1">
-        <v>28</v>
-      </c>
-      <c r="E97" s="1">
-        <v>31</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1">
@@ -5753,41 +5660,41 @@
         <v>5</v>
       </c>
       <c r="B98" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C98" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D98" s="1">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E98" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F98" s="6"/>
       <c r="G98" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1">
       <c r="A99" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B99" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C99" s="1">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D99" s="1">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E99" s="1">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F99" s="6"/>
       <c r="G99" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1">
@@ -5795,125 +5702,125 @@
         <v>2</v>
       </c>
       <c r="B100" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C100" s="1">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D100" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E100" s="1">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F100" s="6"/>
       <c r="G100" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1">
       <c r="A101" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B101" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C101" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D101" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E101" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1">
       <c r="A102" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B102" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C102" s="1">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D102" s="1">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E102" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F102" s="6"/>
       <c r="G102" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1">
       <c r="A103" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B103" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C103" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D103" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E103" s="1">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F103" s="6"/>
       <c r="G103" s="14">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1">
       <c r="A104" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B104" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C104" s="1">
         <v>10</v>
       </c>
       <c r="D104" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E104" s="1">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F104" s="6"/>
       <c r="G104" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1">
       <c r="A105" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B105" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C105" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D105" s="1">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E105" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1">
@@ -5921,356 +5828,356 @@
         <v>1</v>
       </c>
       <c r="B106" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C106" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D106" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E106" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1">
       <c r="A107" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B107" s="1">
         <v>8</v>
       </c>
       <c r="C107" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D107" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E107" s="1">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F107" s="6"/>
       <c r="G107" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1">
       <c r="A108" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B108" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C108" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D108" s="1">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E108" s="1">
         <v>33</v>
       </c>
       <c r="F108" s="6"/>
       <c r="G108" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1">
       <c r="A109" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B109" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C109" s="1">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D109" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E109" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F109" s="6"/>
       <c r="G109" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1">
       <c r="A110" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B110" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C110" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D110" s="1">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E110" s="1">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F110" s="6"/>
       <c r="G110" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1">
       <c r="A111" s="1">
+        <v>1</v>
+      </c>
+      <c r="B111" s="1">
+        <v>2</v>
+      </c>
+      <c r="C111" s="1">
+        <v>4</v>
+      </c>
+      <c r="D111" s="1">
         <v>7</v>
       </c>
-      <c r="B111" s="1">
-        <v>15</v>
-      </c>
-      <c r="C111" s="1">
+      <c r="E111" s="1">
         <v>16</v>
-      </c>
-      <c r="D111" s="1">
-        <v>26</v>
-      </c>
-      <c r="E111" s="1">
-        <v>30</v>
       </c>
       <c r="F111" s="6"/>
       <c r="G111" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1">
       <c r="A112" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B112" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C112" s="1">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D112" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E112" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F112" s="6"/>
       <c r="G112" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1">
       <c r="A113" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B113" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C113" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D113" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E113" s="1">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F113" s="6"/>
       <c r="G113" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1">
       <c r="A114" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B114" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C114" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D114" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E114" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1">
       <c r="A115" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B115" s="1">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C115" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D115" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E115" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1">
       <c r="A116" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B116" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C116" s="1">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D116" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E116" s="1">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1">
       <c r="A117" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B117" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C117" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D117" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E117" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1">
       <c r="A118" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B118" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C118" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D118" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E118" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1">
       <c r="A119" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B119" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C119" s="1">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D119" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E119" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="14">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1">
       <c r="A120" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B120" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C120" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D120" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E120" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1">
       <c r="A121" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B121" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C121" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D121" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E121" s="1">
         <v>26</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1">
       <c r="A122" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B122" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C122" s="1">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D122" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E122" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1">
@@ -6278,20 +6185,20 @@
         <v>1</v>
       </c>
       <c r="B123" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C123" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D123" s="1">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E123" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1">
@@ -6299,118 +6206,118 @@
         <v>1</v>
       </c>
       <c r="B124" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D124" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E124" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F124" s="6"/>
       <c r="G124" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1">
       <c r="A125" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B125" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C125" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D125" s="1">
         <v>22</v>
       </c>
       <c r="E125" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1">
       <c r="A126" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B126" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C126" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D126" s="1">
         <v>22</v>
       </c>
       <c r="E126" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1">
       <c r="A127" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B127" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C127" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D127" s="1">
         <v>22</v>
       </c>
       <c r="E127" s="1">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1">
       <c r="A128" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B128" s="1">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C128" s="1">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D128" s="1">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E128" s="1">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F128" s="6"/>
       <c r="G128" s="14">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1">
       <c r="A129" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B129" s="1">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C129" s="1">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D129" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E129" s="1">
         <v>33</v>
@@ -6422,191 +6329,191 @@
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1">
       <c r="A130" s="1">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B130" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C130" s="1">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D130" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E130" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1">
       <c r="A131" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B131" s="1">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C131" s="1">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D131" s="1">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E131" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1">
       <c r="A132" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B132" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C132" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D132" s="1">
         <v>23</v>
       </c>
       <c r="E132" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1">
       <c r="A133" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B133" s="1">
         <v>15</v>
       </c>
       <c r="C133" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D133" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E133" s="1">
         <v>32</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1">
       <c r="A134" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B134" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C134" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D134" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E134" s="1">
         <v>32</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1">
       <c r="A135" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B135" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C135" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D135" s="1">
         <v>26</v>
       </c>
       <c r="E135" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1">
       <c r="A136" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B136" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C136" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D136" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E136" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1">
       <c r="A137" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B137" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C137" s="1">
+        <v>22</v>
+      </c>
+      <c r="D137" s="1">
         <v>25</v>
-      </c>
-      <c r="D137" s="1">
-        <v>28</v>
       </c>
       <c r="E137" s="1">
         <v>32</v>
       </c>
       <c r="F137" s="6"/>
       <c r="G137" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1">
       <c r="A138" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B138" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C138" s="1">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D138" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E138" s="1">
         <v>32</v>
       </c>
       <c r="F138" s="6"/>
       <c r="G138" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15" thickBot="1">
@@ -6614,104 +6521,104 @@
         <v>5</v>
       </c>
       <c r="B139" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C139" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D139" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E139" s="1">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="15" thickBot="1">
       <c r="A140" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B140" s="1">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C140" s="1">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D140" s="1">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E140" s="1">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F140" s="6"/>
       <c r="G140" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="15" thickBot="1">
       <c r="A141" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B141" s="1">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C141" s="1">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D141" s="1">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E141" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F141" s="6"/>
       <c r="G141" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="15" thickBot="1">
       <c r="A142" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B142" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C142" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D142" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E142" s="1">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="15" thickBot="1">
       <c r="A143" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B143" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C143" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D143" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E143" s="1">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F143" s="6"/>
       <c r="G143" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15" thickBot="1">
@@ -6719,125 +6626,125 @@
         <v>3</v>
       </c>
       <c r="B144" s="1">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C144" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D144" s="1">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E144" s="1">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15" thickBot="1">
       <c r="A145" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B145" s="1">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C145" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D145" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E145" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F145" s="6"/>
       <c r="G145" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15" thickBot="1">
       <c r="A146" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B146" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C146" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D146" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E146" s="1">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15" thickBot="1">
       <c r="A147" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B147" s="1">
         <v>20</v>
       </c>
       <c r="C147" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D147" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E147" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F147" s="6"/>
       <c r="G147" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15" thickBot="1">
       <c r="A148" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B148" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C148" s="1">
+        <v>24</v>
+      </c>
+      <c r="D148" s="1">
         <v>26</v>
       </c>
-      <c r="D148" s="1">
-        <v>31</v>
-      </c>
       <c r="E148" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F148" s="6"/>
       <c r="G148" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="15" thickBot="1">
       <c r="A149" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B149" s="1">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C149" s="1">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D149" s="1">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E149" s="1">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F149" s="6"/>
       <c r="G149" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15" thickBot="1">
@@ -6845,37 +6752,37 @@
         <v>2</v>
       </c>
       <c r="B150" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C150" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D150" s="1">
         <v>17</v>
       </c>
       <c r="E150" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F150" s="6"/>
       <c r="G150" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15" thickBot="1">
       <c r="A151" s="1">
+        <v>2</v>
+      </c>
+      <c r="B151" s="1">
         <v>10</v>
       </c>
-      <c r="B151" s="1">
-        <v>13</v>
-      </c>
       <c r="C151" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D151" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E151" s="1">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F151" s="6"/>
       <c r="G151" s="14">
@@ -6884,166 +6791,166 @@
     </row>
     <row r="152" spans="1:7" ht="15" thickBot="1">
       <c r="A152" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B152" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C152" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D152" s="1">
         <v>27</v>
       </c>
       <c r="E152" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F152" s="6"/>
       <c r="G152" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1">
       <c r="A153" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B153" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C153" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D153" s="1">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E153" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F153" s="6"/>
       <c r="G153" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1">
       <c r="A154" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B154" s="1">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C154" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D154" s="1">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E154" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F154" s="6"/>
       <c r="G154" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1">
       <c r="A155" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B155" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C155" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D155" s="1">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E155" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F155" s="6"/>
       <c r="G155" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1">
       <c r="A156" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B156" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C156" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D156" s="1">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E156" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1">
       <c r="A157" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B157" s="1">
         <v>9</v>
       </c>
       <c r="C157" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D157" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E157" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F157" s="6"/>
       <c r="G157" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1">
       <c r="A158" s="1">
+        <v>6</v>
+      </c>
+      <c r="B158" s="1">
         <v>9</v>
       </c>
-      <c r="B158" s="1">
-        <v>14</v>
-      </c>
       <c r="C158" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D158" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E158" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F158" s="6"/>
       <c r="G158" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1">
       <c r="A159" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B159" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C159" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D159" s="1">
         <v>31</v>
       </c>
       <c r="E159" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F159" s="6"/>
       <c r="G159" s="14">
@@ -7052,19 +6959,19 @@
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1">
       <c r="A160" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B160" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C160" s="1">
+        <v>22</v>
+      </c>
+      <c r="D160" s="1">
+        <v>31</v>
+      </c>
+      <c r="E160" s="1">
         <v>32</v>
-      </c>
-      <c r="D160" s="1">
-        <v>33</v>
-      </c>
-      <c r="E160" s="1">
-        <v>34</v>
       </c>
       <c r="F160" s="6"/>
       <c r="G160" s="14">
@@ -7073,74 +6980,95 @@
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1">
       <c r="A161" s="1">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B161" s="1">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C161" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D161" s="1">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E161" s="1">
         <v>34</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1">
       <c r="A162" s="1">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B162" s="1">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C162" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D162" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E162" s="1">
         <v>34</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1">
       <c r="A163" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B163" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C163" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D163" s="1">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E163" s="1">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15" thickBot="1">
+      <c r="A164" s="1">
+        <v>1</v>
+      </c>
+      <c r="B164" s="1">
+        <v>5</v>
+      </c>
+      <c r="C164" s="1">
+        <v>8</v>
+      </c>
+      <c r="D164" s="1">
+        <v>13</v>
+      </c>
+      <c r="E164" s="1">
+        <v>19</v>
+      </c>
+      <c r="F164" s="6"/>
+      <c r="G164" s="14">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F6:F1048576">
+  <conditionalFormatting sqref="F7:F1048576">
     <cfRule type="cellIs" dxfId="15" priority="10" operator="equal">
       <formula>38</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:L4 N4:R4 H6:L6 N6:R6 H8:L8 N8:R8 H10:I10 N10:O10">
+  <conditionalFormatting sqref="H5:L5 N5:R5 H7:L7 N7:R7 H9:L9 N9:R9 H11:I11 N11:O11">
     <cfRule type="cellIs" dxfId="14" priority="6" operator="lessThanOrEqual">
       <formula>20</formula>
     </cfRule>
@@ -7152,7 +7080,7 @@
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J10:L10">
+  <conditionalFormatting sqref="J11:L11">
     <cfRule type="cellIs" dxfId="11" priority="29" operator="greaterThanOrEqual">
       <formula>60</formula>
     </cfRule>
@@ -7164,7 +7092,7 @@
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P10:R10">
+  <conditionalFormatting sqref="P11:R11">
     <cfRule type="cellIs" dxfId="8" priority="32" operator="greaterThanOrEqual">
       <formula>60</formula>
     </cfRule>
@@ -7553,12 +7481,8 @@
       <c r="A2" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="M2" s="63" t="s">
-        <v>224</v>
-      </c>
+      <c r="L2" s="62"/>
+      <c r="M2" s="63"/>
       <c r="N2" s="64"/>
       <c r="O2" s="65"/>
     </row>
@@ -7570,12 +7494,8 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="L3" s="66" t="s">
-        <v>225</v>
-      </c>
-      <c r="M3" s="60" t="s">
-        <v>225</v>
-      </c>
+      <c r="L3" s="73"/>
+      <c r="M3" s="74"/>
       <c r="N3" s="60"/>
       <c r="O3" s="67"/>
     </row>
@@ -7584,12 +7504,8 @@
         <v>187</v>
       </c>
       <c r="K4" s="68"/>
-      <c r="L4" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="M4" s="60" t="s">
-        <v>226</v>
-      </c>
+      <c r="L4" s="73"/>
+      <c r="M4" s="74"/>
       <c r="N4" s="60"/>
       <c r="O4" s="67"/>
     </row>
@@ -7623,12 +7539,8 @@
         <v>189</v>
       </c>
       <c r="K6" s="68"/>
-      <c r="L6" s="68" t="s">
-        <v>227</v>
-      </c>
-      <c r="M6" t="s">
-        <v>202</v>
-      </c>
+      <c r="L6" s="70"/>
+      <c r="M6" s="3"/>
       <c r="N6"/>
     </row>
     <row r="7" spans="1:21">
@@ -7636,12 +7548,8 @@
         <v>190</v>
       </c>
       <c r="K7" s="68"/>
-      <c r="L7" s="68" t="s">
-        <v>228</v>
-      </c>
-      <c r="M7" t="s">
-        <v>203</v>
-      </c>
+      <c r="L7" s="70"/>
+      <c r="M7" s="3"/>
       <c r="N7"/>
     </row>
     <row r="8" spans="1:21">
@@ -7668,12 +7576,8 @@
       <c r="I9" s="24"/>
       <c r="J9" s="24"/>
       <c r="K9" s="68"/>
-      <c r="L9" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="M9" s="51" t="s">
-        <v>230</v>
-      </c>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
       <c r="N9" s="61"/>
       <c r="O9" s="67"/>
       <c r="P9" s="24"/>
@@ -7696,12 +7600,8 @@
         <v>141</v>
       </c>
       <c r="K11" s="68"/>
-      <c r="L11" t="s">
-        <v>214</v>
-      </c>
-      <c r="M11" t="s">
-        <v>214</v>
-      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
       <c r="N11"/>
     </row>
     <row r="12" spans="1:21">
@@ -7709,12 +7609,8 @@
         <v>193</v>
       </c>
       <c r="K12" s="68"/>
-      <c r="L12" t="s">
-        <v>215</v>
-      </c>
-      <c r="M12" t="s">
-        <v>215</v>
-      </c>
+      <c r="L12"/>
+      <c r="M12"/>
       <c r="N12"/>
     </row>
     <row r="13" spans="1:21">
@@ -7729,13 +7625,9 @@
       <c r="A14" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="K14" s="68"/>
-      <c r="L14" t="s">
-        <v>135</v>
-      </c>
-      <c r="M14" t="s">
-        <v>135</v>
-      </c>
+      <c r="K14" s="70"/>
+      <c r="L14" s="3"/>
+      <c r="M14"/>
       <c r="N14" s="61"/>
       <c r="O14" s="67"/>
     </row>
@@ -7743,13 +7635,9 @@
       <c r="A15" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="K15" s="66"/>
-      <c r="L15" t="s">
-        <v>217</v>
-      </c>
-      <c r="M15" t="s">
-        <v>217</v>
-      </c>
+      <c r="K15" s="73"/>
+      <c r="L15"/>
+      <c r="M15"/>
       <c r="N15" s="61"/>
       <c r="O15" s="67"/>
     </row>
@@ -7757,13 +7645,9 @@
       <c r="A16" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K16" s="66"/>
-      <c r="L16" t="s">
-        <v>218</v>
-      </c>
-      <c r="M16" t="s">
-        <v>218</v>
-      </c>
+      <c r="K16" s="73"/>
+      <c r="L16"/>
+      <c r="M16" s="3"/>
       <c r="N16" s="61"/>
       <c r="O16" s="67"/>
     </row>
@@ -7771,13 +7655,9 @@
       <c r="A17" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="K17" s="66"/>
-      <c r="L17" t="s">
-        <v>219</v>
-      </c>
-      <c r="M17" t="s">
-        <v>219</v>
-      </c>
+      <c r="K17" s="73"/>
+      <c r="L17"/>
+      <c r="M17"/>
       <c r="N17" s="61"/>
       <c r="O17" s="67"/>
     </row>
@@ -7785,7 +7665,7 @@
       <c r="A18" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K18" s="66"/>
+      <c r="K18" s="73"/>
       <c r="L18" s="68"/>
       <c r="M18" s="61"/>
       <c r="N18" s="61"/>
@@ -7793,13 +7673,9 @@
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1">
       <c r="A19" s="4"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="61" t="s">
-        <v>229</v>
-      </c>
-      <c r="M19" s="61" t="s">
-        <v>229</v>
-      </c>
+      <c r="K19" s="73"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
       <c r="N19" s="61"/>
       <c r="O19" s="67"/>
     </row>
@@ -7807,13 +7683,9 @@
       <c r="A20" t="s">
         <v>136</v>
       </c>
-      <c r="K20" s="44"/>
-      <c r="L20" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="M20" s="63" t="s">
-        <v>224</v>
-      </c>
+      <c r="K20" s="76"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="63"/>
       <c r="N20" s="61"/>
       <c r="O20" s="67"/>
     </row>
@@ -7821,7 +7693,7 @@
       <c r="A21" t="s">
         <v>200</v>
       </c>
-      <c r="K21" s="4"/>
+      <c r="K21" s="75"/>
       <c r="L21" s="68"/>
       <c r="M21" s="61"/>
       <c r="N21" s="61"/>
@@ -7831,13 +7703,8 @@
       <c r="A22" t="s">
         <v>201</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="68" t="s">
-        <v>231</v>
-      </c>
-      <c r="M22" s="68" t="s">
-        <v>242</v>
-      </c>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
       <c r="N22" s="61"/>
       <c r="O22" s="67"/>
     </row>
@@ -7845,13 +7712,8 @@
       <c r="A23" t="s">
         <v>202</v>
       </c>
-      <c r="K23" s="51"/>
-      <c r="L23" s="68" t="s">
-        <v>232</v>
-      </c>
-      <c r="M23" s="68" t="s">
-        <v>243</v>
-      </c>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
       <c r="N23" s="61"/>
       <c r="O23" s="67"/>
     </row>
@@ -7859,13 +7721,8 @@
       <c r="A24" t="s">
         <v>203</v>
       </c>
-      <c r="K24" s="51"/>
-      <c r="L24" s="68" t="s">
-        <v>233</v>
-      </c>
-      <c r="M24" s="68" t="s">
-        <v>244</v>
-      </c>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
       <c r="N24" s="61"/>
       <c r="O24" s="67"/>
     </row>
@@ -7873,13 +7730,8 @@
       <c r="A25" t="s">
         <v>204</v>
       </c>
-      <c r="K25" s="51"/>
-      <c r="L25" s="68" t="s">
-        <v>234</v>
-      </c>
-      <c r="M25" s="68" t="s">
-        <v>245</v>
-      </c>
+      <c r="L25" s="70"/>
+      <c r="M25" s="68"/>
       <c r="N25" s="61"/>
       <c r="O25" s="67"/>
     </row>
@@ -7887,7 +7739,6 @@
       <c r="A26" t="s">
         <v>205</v>
       </c>
-      <c r="K26" s="51"/>
       <c r="L26" s="68"/>
       <c r="M26" s="61"/>
       <c r="N26" s="61"/>
@@ -7897,22 +7748,16 @@
       <c r="A27" t="s">
         <v>206</v>
       </c>
-      <c r="K27" s="51"/>
-      <c r="L27" s="68" t="s">
-        <v>235</v>
-      </c>
-      <c r="M27" s="68" t="s">
-        <v>246</v>
-      </c>
+      <c r="K27" s="75"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
       <c r="N27" s="61"/>
       <c r="O27" s="67"/>
     </row>
     <row r="28" spans="1:15">
       <c r="K28" s="51"/>
       <c r="L28" s="68"/>
-      <c r="M28" s="68" t="s">
-        <v>247</v>
-      </c>
+      <c r="M28" s="68"/>
       <c r="N28" s="61"/>
       <c r="O28" s="67"/>
     </row>
@@ -7920,13 +7765,9 @@
       <c r="A29" t="s">
         <v>142</v>
       </c>
-      <c r="K29" s="51"/>
-      <c r="L29" s="66" t="s">
-        <v>240</v>
-      </c>
-      <c r="M29" s="68" t="s">
-        <v>248</v>
-      </c>
+      <c r="K29" s="71"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="68"/>
       <c r="N29" s="61"/>
       <c r="O29" s="67"/>
     </row>
@@ -7935,9 +7776,7 @@
         <v>207</v>
       </c>
       <c r="K30" s="51"/>
-      <c r="L30" s="51" t="s">
-        <v>241</v>
-      </c>
+      <c r="L30" s="71"/>
       <c r="M30" s="61"/>
       <c r="N30" s="61"/>
       <c r="O30" s="67"/>
@@ -7946,11 +7785,9 @@
       <c r="A31" t="s">
         <v>208</v>
       </c>
-      <c r="K31" s="51"/>
+      <c r="K31" s="71"/>
       <c r="L31" s="68"/>
-      <c r="M31" s="66" t="s">
-        <v>253</v>
-      </c>
+      <c r="M31" s="73"/>
       <c r="N31" s="61"/>
       <c r="O31" s="67"/>
     </row>
@@ -7959,21 +7796,15 @@
         <v>209</v>
       </c>
       <c r="K32" s="51"/>
-      <c r="L32" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="M32" s="61"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="72"/>
       <c r="N32" s="61"/>
       <c r="O32" s="67"/>
     </row>
     <row r="33" spans="1:15">
       <c r="K33" s="51"/>
-      <c r="L33" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="M33" s="51" t="s">
-        <v>254</v>
-      </c>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
       <c r="N33" s="61"/>
       <c r="O33" s="67"/>
     </row>
@@ -7982,12 +7813,7 @@
         <v>143</v>
       </c>
       <c r="K34" s="51"/>
-      <c r="L34" s="51" t="s">
-        <v>238</v>
-      </c>
-      <c r="M34" s="51" t="s">
-        <v>255</v>
-      </c>
+      <c r="L34" s="71"/>
       <c r="N34" s="60"/>
       <c r="O34" s="67"/>
     </row>
@@ -7996,9 +7822,7 @@
         <v>135</v>
       </c>
       <c r="K35" s="51"/>
-      <c r="L35" s="51" t="s">
-        <v>239</v>
-      </c>
+      <c r="L35" s="71"/>
       <c r="M35" s="61"/>
       <c r="N35" s="60"/>
       <c r="O35" s="67"/>
@@ -8009,9 +7833,7 @@
       </c>
       <c r="K36" s="51"/>
       <c r="L36" s="66"/>
-      <c r="M36" s="51" t="s">
-        <v>249</v>
-      </c>
+      <c r="M36" s="71"/>
       <c r="N36" s="61"/>
       <c r="O36" s="67"/>
     </row>
@@ -8021,9 +7843,7 @@
       </c>
       <c r="K37" s="51"/>
       <c r="L37" s="44"/>
-      <c r="M37" s="51" t="s">
-        <v>250</v>
-      </c>
+      <c r="M37" s="71"/>
       <c r="N37" s="69"/>
       <c r="O37" s="25"/>
     </row>
@@ -8033,16 +7853,10 @@
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="4"/>
-      <c r="M38" s="51" t="s">
-        <v>251</v>
-      </c>
     </row>
     <row r="39" spans="1:15">
       <c r="K39" s="51"/>
       <c r="L39" s="4"/>
-      <c r="M39" s="51" t="s">
-        <v>252</v>
-      </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
@@ -8149,7 +7963,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31846DB-4BC4-4837-86F6-698F590C512A}">
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
@@ -8163,162 +7977,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1">
-      <c r="A1">
-        <v>5</v>
+      <c r="A1" s="14">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" thickBot="1">
       <c r="A2" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" thickBot="1">
       <c r="A3" s="14">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" thickBot="1">
       <c r="A4" s="14">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1">
       <c r="A5" s="14">
-        <v>9</v>
-      </c>
-      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" thickBot="1">
       <c r="A6" s="14">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1">
+      <c r="A7" s="14">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <f>COUNTIF($A:$A,1)</f>
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <f>COUNTIF($A:$A,3)</f>
         <v>14</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <f>COUNTIF($A:$A,5)</f>
         <v>14</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <f>COUNTIF($A:$A,7)</f>
         <v>8</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <f>COUNTIF($A:$A,9)</f>
-        <v>13</v>
-      </c>
-      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="I7">
         <f>COUNTIF($A:$A,2)</f>
         <v>13</v>
       </c>
-      <c r="J6">
+      <c r="J7">
         <f>COUNTIF($A:$A,4)</f>
         <v>9</v>
       </c>
-      <c r="K6">
+      <c r="K7">
         <f>COUNTIF($A:$A,6)</f>
         <v>9</v>
       </c>
-      <c r="L6">
+      <c r="L7">
         <f>COUNTIF($A:$A,8)</f>
         <v>13</v>
       </c>
-      <c r="M6">
+      <c r="M7">
         <f>COUNTIF($A:$A,10)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1">
-      <c r="A7" s="14">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-    </row>
     <row r="8" spans="1:13" ht="15" thickBot="1">
       <c r="A8" s="14">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>13</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" thickBot="1">
+      <c r="A9" s="14">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <f>COUNTIF($A:$A,11)</f>
         <v>7</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <f>COUNTIF($A:$A,13)</f>
         <v>12</v>
       </c>
-      <c r="I8">
+      <c r="I9">
         <f>COUNTIF($A:$A,12)</f>
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <f>COUNTIF($A:$A,14)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" thickBot="1">
-      <c r="A9" s="14">
-        <v>11</v>
-      </c>
-    </row>
     <row r="10" spans="1:13" ht="15" thickBot="1">
       <c r="A10" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" thickBot="1">
       <c r="A11" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" thickBot="1">
@@ -8328,37 +8142,37 @@
     </row>
     <row r="13" spans="1:13" ht="15" thickBot="1">
       <c r="A13" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" thickBot="1">
       <c r="A14" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" thickBot="1">
       <c r="A15" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" thickBot="1">
       <c r="A16" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" thickBot="1">
       <c r="A17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" thickBot="1">
       <c r="A18" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" thickBot="1">
       <c r="A19" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" thickBot="1">
@@ -8368,22 +8182,22 @@
     </row>
     <row r="21" spans="1:1" ht="15" thickBot="1">
       <c r="A21" s="14">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" thickBot="1">
       <c r="A22" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" thickBot="1">
       <c r="A23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" thickBot="1">
       <c r="A24" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15" thickBot="1">
@@ -8393,47 +8207,47 @@
     </row>
     <row r="26" spans="1:1" ht="15" thickBot="1">
       <c r="A26" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" thickBot="1">
       <c r="A27" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15" thickBot="1">
       <c r="A28" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15" thickBot="1">
       <c r="A29" s="14">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" thickBot="1">
       <c r="A30" s="14">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15" thickBot="1">
       <c r="A31" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15" thickBot="1">
       <c r="A32" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" thickBot="1">
       <c r="A33" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" thickBot="1">
       <c r="A34" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" thickBot="1">
@@ -8443,32 +8257,32 @@
     </row>
     <row r="36" spans="1:1" ht="15" thickBot="1">
       <c r="A36" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15" thickBot="1">
       <c r="A37" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15" thickBot="1">
       <c r="A38" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15" thickBot="1">
       <c r="A39" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15" thickBot="1">
       <c r="A40" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15" thickBot="1">
       <c r="A41" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15" thickBot="1">
@@ -8478,47 +8292,47 @@
     </row>
     <row r="43" spans="1:1" ht="15" thickBot="1">
       <c r="A43" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15" thickBot="1">
       <c r="A44" s="14">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15" thickBot="1">
       <c r="A45" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15" thickBot="1">
       <c r="A46" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15" thickBot="1">
       <c r="A47" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="15" thickBot="1">
       <c r="A48" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15" thickBot="1">
       <c r="A49" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15" thickBot="1">
       <c r="A50" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15" thickBot="1">
       <c r="A51" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15" thickBot="1">
@@ -8528,72 +8342,72 @@
     </row>
     <row r="53" spans="1:1" ht="15" thickBot="1">
       <c r="A53" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="15" thickBot="1">
       <c r="A54" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="15" thickBot="1">
       <c r="A55" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="15" thickBot="1">
       <c r="A56" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="15" thickBot="1">
       <c r="A57" s="14">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="15" thickBot="1">
       <c r="A58" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="15" thickBot="1">
       <c r="A59" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="15" thickBot="1">
       <c r="A60" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="15" thickBot="1">
       <c r="A61" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="15" thickBot="1">
       <c r="A62" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="15" thickBot="1">
       <c r="A63" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="15" thickBot="1">
       <c r="A64" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15" thickBot="1">
       <c r="A65" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="15" thickBot="1">
       <c r="A66" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15" thickBot="1">
@@ -8603,242 +8417,242 @@
     </row>
     <row r="68" spans="1:1" ht="15" thickBot="1">
       <c r="A68" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="15" thickBot="1">
       <c r="A69" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="15" thickBot="1">
       <c r="A70" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15" thickBot="1">
       <c r="A71" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="15" thickBot="1">
       <c r="A72" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="15" thickBot="1">
       <c r="A73" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="15" thickBot="1">
       <c r="A74" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15" thickBot="1">
       <c r="A75" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="15" thickBot="1">
       <c r="A76" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="15" thickBot="1">
       <c r="A77" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="15" thickBot="1">
       <c r="A78" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="15" thickBot="1">
       <c r="A79" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="15" thickBot="1">
       <c r="A80" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="15" thickBot="1">
       <c r="A81" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="15" thickBot="1">
       <c r="A82" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="15" thickBot="1">
       <c r="A83" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="15" thickBot="1">
       <c r="A84" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="15" thickBot="1">
       <c r="A85" s="14">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="15" thickBot="1">
       <c r="A86" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="15" thickBot="1">
       <c r="A87" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="15" thickBot="1">
       <c r="A88" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="15" thickBot="1">
       <c r="A89" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="15" thickBot="1">
       <c r="A90" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="15" thickBot="1">
       <c r="A91" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="15" thickBot="1">
       <c r="A92" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="15" thickBot="1">
       <c r="A93" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="15" thickBot="1">
       <c r="A94" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="15" thickBot="1">
       <c r="A95" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="15" thickBot="1">
       <c r="A96" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="15" thickBot="1">
       <c r="A97" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="15" thickBot="1">
       <c r="A98" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="15" thickBot="1">
       <c r="A99" s="14">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="15" thickBot="1">
       <c r="A100" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="15" thickBot="1">
       <c r="A101" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="15" thickBot="1">
       <c r="A102" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="15" thickBot="1">
       <c r="A103" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="15" thickBot="1">
       <c r="A104" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="15" thickBot="1">
       <c r="A105" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="15" thickBot="1">
       <c r="A106" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="15" thickBot="1">
       <c r="A107" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="15" thickBot="1">
       <c r="A108" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="15" thickBot="1">
       <c r="A109" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="15" thickBot="1">
       <c r="A110" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:1" ht="15" thickBot="1">
       <c r="A111" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:1" ht="15" thickBot="1">
       <c r="A112" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="15" thickBot="1">
       <c r="A113" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="15" thickBot="1">
       <c r="A114" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="15" thickBot="1">
       <c r="A115" s="14">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="15" thickBot="1">
@@ -8848,47 +8662,47 @@
     </row>
     <row r="117" spans="1:1" ht="15" thickBot="1">
       <c r="A117" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:1" ht="15" thickBot="1">
       <c r="A118" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:1" ht="15" thickBot="1">
       <c r="A119" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="15" thickBot="1">
       <c r="A120" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:1" ht="15" thickBot="1">
       <c r="A121" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="15" thickBot="1">
       <c r="A122" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="15" thickBot="1">
       <c r="A123" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:1" ht="15" thickBot="1">
       <c r="A124" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="15" thickBot="1">
       <c r="A125" s="14">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:1" ht="15" thickBot="1">
@@ -8898,107 +8712,107 @@
     </row>
     <row r="127" spans="1:1" ht="15" thickBot="1">
       <c r="A127" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:1" ht="15" thickBot="1">
       <c r="A128" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="15" thickBot="1">
       <c r="A129" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="15" thickBot="1">
       <c r="A130" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="15" thickBot="1">
       <c r="A131" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="15" thickBot="1">
       <c r="A132" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="15" thickBot="1">
       <c r="A133" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="15" thickBot="1">
       <c r="A134" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="15" thickBot="1">
       <c r="A135" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="15" thickBot="1">
       <c r="A136" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="15" thickBot="1">
       <c r="A137" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="15" thickBot="1">
       <c r="A138" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="15" thickBot="1">
       <c r="A139" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="15" thickBot="1">
       <c r="A140" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="15" thickBot="1">
       <c r="A141" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="15" thickBot="1">
       <c r="A142" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="15" thickBot="1">
       <c r="A143" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="15" thickBot="1">
       <c r="A144" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="15" thickBot="1">
       <c r="A145" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="15" thickBot="1">
       <c r="A146" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="15" thickBot="1">
       <c r="A147" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="15" thickBot="1">
@@ -9008,37 +8822,37 @@
     </row>
     <row r="149" spans="1:1" ht="15" thickBot="1">
       <c r="A149" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:1" ht="15" thickBot="1">
       <c r="A150" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:1" ht="15" thickBot="1">
       <c r="A151" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="15" thickBot="1">
       <c r="A152" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:1" ht="15" thickBot="1">
       <c r="A153" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="15" thickBot="1">
       <c r="A154" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="15" thickBot="1">
       <c r="A155" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="15" thickBot="1">
@@ -9053,21 +8867,26 @@
     </row>
     <row r="158" spans="1:1" ht="15" thickBot="1">
       <c r="A158" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:1" ht="15" thickBot="1">
       <c r="A159" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160" spans="1:1" ht="15" thickBot="1">
       <c r="A160" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="15" thickBot="1">
+      <c r="A161" s="14">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:G6 I6:M6 C8:D8 I8:J8">
+  <conditionalFormatting sqref="C7:G7 I7:M7 C9:D9 I9:J9">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThanOrEqual">
       <formula>8</formula>
     </cfRule>
